--- a/moduli_aziende/aifecs/moduli_compilati/Matrice competenze_2026.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/Matrice competenze_2026.xlsx
@@ -2,80 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMM" sheetId="6" r:id="Ra2e372fe2fa742e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RDF" sheetId="4" r:id="R9a16289753ca4360"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPE" sheetId="10" r:id="R54350de3e9644003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPE (2)" sheetId="11" r:id="Rb57571a67ea34397"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMM" sheetId="6" r:id="Rf2609252ee554c6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RDF" sheetId="4" r:id="R4ed7af88c960433f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPE" sheetId="10" r:id="R9ae651ae19ce45ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPE (2)" sheetId="11" r:id="R5c0d50b55b2f4795"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1000,9 +932,8 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0cb1ed3561f4902"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re03053b7b2fc4c4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rede532e1b1c04413"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1097,9 +1028,8 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cacdbf2b58a462c"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra135beb118f1465f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d92b0ff52664d58"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1203,9 +1133,8 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc06b3ba96ecc4045"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9d8e777373a4400"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cf75009d83d4deb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1309,9 +1238,8 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cf27473ea4b4d74"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a10ec611eab4650"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a43c2ff63dd4b7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>